--- a/muban_clean/fushi.xlsx
+++ b/muban_clean/fushi.xlsx
@@ -11,6 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="\P">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'7.4'!$A$1:$I$353</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="267">
   <si>
     <t xml:space="preserve">                                                                                      广东帝豪装饰集团巴中分公司（工程预算单）
 </t>
@@ -1034,113 +1035,6 @@
   <si>
     <t>业主：　　　　　审核：　　　　　　设计师：　　　　　　施工图：　　　　　效果图：　　　　　报价：</t>
   </si>
-  <si>
-    <t>现浇梁(240*300以内）</t>
-  </si>
-  <si>
-    <t>1、钢筋、悬空处理、水泥、砂。</t>
-  </si>
-  <si>
-    <t>现浇楼板</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10MM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>螺纹钢主筋双层双向，10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>MM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>螺纹钢辅筋扎网，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>12MM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模板支架，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>32.5#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水泥现浇。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、人工及机具费。</t>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -1155,7 +1049,7 @@
     <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="60">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1341,11 +1235,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1521,7 +1410,6 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1542,13 +1430,14 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
-      <name val="新宋体"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
-      <name val="宋体"/>
+      <name val="新宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2060,152 +1949,152 @@
   </borders>
   <cellStyleXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2215,20 +2104,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="5">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="14">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="14">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2774,18 +2663,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="66">
@@ -3176,7 +3053,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:FM356"/>
+  <dimension ref="A1:FM353"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.08333333333333" style="26" customWidth="1"/>
@@ -13593,69 +13470,6 @@
       <c r="K353" s="189"/>
       <c r="L353" s="189"/>
     </row>
-    <row r="355" s="21" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A355" s="47">
-        <v>23</v>
-      </c>
-      <c r="B355" s="176" t="s">
-        <v>267</v>
-      </c>
-      <c r="C355" s="47">
-        <f>5.6+28.8</f>
-        <v>34.4</v>
-      </c>
-      <c r="D355" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E355" s="190">
-        <v>280</v>
-      </c>
-      <c r="F355" s="47">
-        <f>C355*E355</f>
-        <v>9632</v>
-      </c>
-      <c r="G355" s="190">
-        <v>180</v>
-      </c>
-      <c r="H355" s="47">
-        <f>SUM(G355*C355)</f>
-        <v>6192</v>
-      </c>
-      <c r="I355" s="48" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="356" customFormat="1" ht="27" customHeight="1" spans="1:12">
-      <c r="A356" s="47">
-        <v>24</v>
-      </c>
-      <c r="B356" s="191" t="s">
-        <v>269</v>
-      </c>
-      <c r="C356" s="47">
-        <v>49.3</v>
-      </c>
-      <c r="D356" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="E356" s="192">
-        <v>340</v>
-      </c>
-      <c r="F356" s="47">
-        <f>C356*E356</f>
-        <v>16762</v>
-      </c>
-      <c r="G356" s="49">
-        <v>380</v>
-      </c>
-      <c r="H356" s="47">
-        <f>SUM(G356*C356)</f>
-        <v>18734</v>
-      </c>
-      <c r="I356" s="193" t="s">
-        <v>270</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="38">
     <mergeCell ref="A1:I1"/>
@@ -13698,10 +13512,13 @@
     <mergeCell ref="G4:H5"/>
   </mergeCells>
   <pageMargins left="0.275" right="0.0777777777777778" top="0.235416666666667" bottom="0.0388888888888889" header="0.829861111111111" footer="0.235416666666667"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="98" orientation="landscape"/>
   <headerFooter alignWithMargins="0" scaleWithDoc="0">
     <oddFooter>&amp;C&amp;"Times New Roman"&amp;12第 &amp;P 页</oddFooter>
   </headerFooter>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="9" max="1048575" man="1"/>
+  </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/muban_clean/fushi.xlsx
+++ b/muban_clean/fushi.xlsx
@@ -89,23 +89,7 @@
     <t>石膏板平面天花</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="新宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
+    <t>M²</t>
   </si>
   <si>
     <t>木龙骨或轻钢龙骨框架结构、膨胀螺丝固定、纸面石膏板封面（以展开面积计算)、乳胶漆另计</t>
@@ -114,25 +98,7 @@
     <t>造型天花</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
+    <t>M²</t>
   </si>
   <si>
     <t>木龙骨或轻钢龙骨框架，造型位置夹板框架、纸面石膏板封面(以展开面积计算)、弧型处夹板衬底、乳胶漆另计。</t>
@@ -165,23 +131,7 @@
     <t>造型基层</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
+    <t>M²</t>
   </si>
   <si>
     <t>木龙骨框架结构，膨胀螺丝固定，欧松板封面刷防潮油、人工及机具费。（***业主自购）</t>
@@ -763,25 +713,7 @@
     <t>墙面防裂网</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
+    <t>M²</t>
   </si>
   <si>
     <t>墙面挂网、人工</t>
